--- a/Sherwood_etal_2004_I/Sherwood_etal_2004_l.xlsx
+++ b/Sherwood_etal_2004_I/Sherwood_etal_2004_l.xlsx
@@ -2355,8 +2355,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1692e213da595cbe2f8b4fd37e6b2a91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="27148b6917a39128a8d85a83794e1a7d" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -2378,10 +2378,6 @@
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2447,26 +2443,6 @@
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
@@ -2636,7 +2612,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A3F681A-B589-408A-BBB1-548FAE410F47}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BDA2607-DD57-497C-96D8-028C1B1410DF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
